--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Constant Maturity Gilt Fund.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Constant Maturity Gilt Fund.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="50">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Constant Maturity Gilt Fund</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -64,22 +64,31 @@
     <t>Government Securities</t>
   </si>
   <si>
+    <t>IN0020240126</t>
+  </si>
+  <si>
+    <t>SOV</t>
+  </si>
+  <si>
+    <t>IN0020210020</t>
+  </si>
+  <si>
     <t>IN0020240019</t>
   </si>
   <si>
-    <t>SOV</t>
-  </si>
-  <si>
     <t>IN0020230077</t>
   </si>
   <si>
-    <t>IN0020240126</t>
+    <t>IN0020200096</t>
   </si>
   <si>
     <t>IN0020240134</t>
   </si>
   <si>
-    <t>IN0020230085</t>
+    <t>IN0020210152</t>
+  </si>
+  <si>
+    <t>IN0020250026</t>
   </si>
   <si>
     <t>Non-Convertible debentures / Bonds</t>
@@ -142,7 +151,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -528,13 +537,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>57</xdr:row>
+      <xdr:row>60</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -552,7 +561,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="11315700"/>
+          <a:off x="666750" y="11887200"/>
           <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -567,13 +576,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>75</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>82</xdr:row>
+      <xdr:row>85</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -591,7 +600,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="14173200"/>
+          <a:off x="666750" y="14744700"/>
           <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -925,7 +934,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J71"/>
+  <dimension ref="B1:J74"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="22" width="10.0" collapsed="true"/>
@@ -933,7 +942,7 @@
     <col min="3" max="3" bestFit="true" customWidth="true" style="22" width="16.0" collapsed="true"/>
     <col min="4" max="4" bestFit="true" customWidth="true" style="22" width="9.714285714285714" collapsed="true"/>
     <col min="5" max="5" bestFit="true" customWidth="true" style="22" width="19.714285714285715" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="22" width="12.571428571428571" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="22" width="11.142857142857142" collapsed="true"/>
     <col min="7" max="7" bestFit="true" customWidth="true" style="22" width="38.714285714285715" collapsed="true"/>
     <col min="8" max="8" bestFit="true" customWidth="true" style="22" width="11.714285714285714" collapsed="true"/>
     <col min="9" max="9" bestFit="true" customWidth="true" style="22" width="29.714285714285715" collapsed="true"/>
@@ -1025,10 +1034,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="9">
-        <v>240738.12999999998</v>
+        <v>247224.51</v>
       </c>
       <c r="H5" s="10">
-        <v>0.9766332015646</v>
+        <v>0.9692167668621</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>13</v>
@@ -1062,10 +1071,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="9">
-        <v>240738.12999999998</v>
+        <v>247224.51</v>
       </c>
       <c r="H7" s="10">
-        <v>0.9766332015646</v>
+        <v>0.9692167668621</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>13</v>
@@ -1099,10 +1108,10 @@
         <v>13</v>
       </c>
       <c r="G9" s="9">
-        <v>240738.12999999998</v>
+        <v>247224.51</v>
       </c>
       <c r="H9" s="10">
-        <v>0.9766332015646</v>
+        <v>0.9692167668621</v>
       </c>
       <c r="I9" s="9" t="s">
         <v>13</v>
@@ -1119,22 +1128,22 @@
         <v>16</v>
       </c>
       <c r="D10" s="14">
-        <v>7.10</v>
+        <v>6.79</v>
       </c>
       <c r="E10" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F10" s="15">
-        <v>206056400</v>
+        <v>89822250</v>
       </c>
       <c r="G10" s="16">
-        <v>211014.94</v>
+        <v>93049.47</v>
       </c>
       <c r="H10" s="17">
-        <v>0.8560513302575</v>
+        <v>0.3647903133538</v>
       </c>
       <c r="I10" s="16">
-        <v>6.86</v>
+        <v>6.37</v>
       </c>
       <c r="J10" s="11" t="s">
         <v>13</v>
@@ -1148,22 +1157,22 @@
         <v>18</v>
       </c>
       <c r="D11" s="14">
-        <v>7.18</v>
+        <v>6.640000000000001</v>
       </c>
       <c r="E11" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F11" s="15">
-        <v>18500000</v>
+        <v>63500000</v>
       </c>
       <c r="G11" s="16">
-        <v>19021.94</v>
+        <v>65151.32</v>
       </c>
       <c r="H11" s="17">
-        <v>0.0771687400004</v>
+        <v>0.2554186545954</v>
       </c>
       <c r="I11" s="16">
-        <v>6.96</v>
+        <v>6.39</v>
       </c>
       <c r="J11" s="11" t="s">
         <v>13</v>
@@ -1177,22 +1186,22 @@
         <v>19</v>
       </c>
       <c r="D12" s="14">
-        <v>6.79</v>
+        <v>7.10</v>
       </c>
       <c r="E12" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F12" s="15">
-        <v>7049300</v>
+        <v>60272100</v>
       </c>
       <c r="G12" s="16">
-        <v>7095.80</v>
+        <v>63537.64</v>
       </c>
       <c r="H12" s="17">
-        <v>0.0287864405678</v>
+        <v>0.2490923978972</v>
       </c>
       <c r="I12" s="16">
-        <v>6.81</v>
+        <v>6.39</v>
       </c>
       <c r="J12" s="11" t="s">
         <v>13</v>
@@ -1206,22 +1215,22 @@
         <v>20</v>
       </c>
       <c r="D13" s="14">
-        <v>6.92</v>
+        <v>7.18</v>
       </c>
       <c r="E13" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F13" s="15">
-        <v>3500000</v>
+        <v>14000000</v>
       </c>
       <c r="G13" s="16">
-        <v>3530.86</v>
+        <v>14910.48</v>
       </c>
       <c r="H13" s="17">
-        <v>0.0143240919337</v>
+        <v>0.0584549129775</v>
       </c>
       <c r="I13" s="16">
-        <v>6.94</v>
+        <v>6.50</v>
       </c>
       <c r="J13" s="11" t="s">
         <v>13</v>
@@ -1235,22 +1244,22 @@
         <v>21</v>
       </c>
       <c r="D14" s="14">
-        <v>7.18</v>
+        <v>6.19</v>
       </c>
       <c r="E14" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F14" s="15">
-        <v>72600</v>
+        <v>5000000</v>
       </c>
       <c r="G14" s="16">
-        <v>74.59</v>
+        <v>4965.30</v>
       </c>
       <c r="H14" s="17">
-        <v>0.0003025988052</v>
+        <v>0.0194659178918</v>
       </c>
       <c r="I14" s="16">
-        <v>6.87</v>
+        <v>6.39</v>
       </c>
       <c r="J14" s="11" t="s">
         <v>13</v>
@@ -1258,36 +1267,57 @@
     </row>
     <row r="15" spans="2:10" ht="15" customHeight="1">
       <c r="B15" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="14">
+        <v>6.92</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F15" s="15">
+        <v>2500000</v>
+      </c>
+      <c r="G15" s="16">
+        <v>2617.66</v>
+      </c>
+      <c r="H15" s="17">
+        <v>0.0102622509473</v>
+      </c>
+      <c r="I15" s="16">
+        <v>6.52</v>
       </c>
       <c r="J15" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="16" spans="2:10" ht="15" customHeight="1">
-      <c r="B16" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G16" s="9" t="s">
+      <c r="B16" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="H16" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="I16" s="9" t="s">
-        <v>13</v>
+      <c r="D16" s="14">
+        <v>6.67</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" s="15">
+        <v>2500000</v>
+      </c>
+      <c r="G16" s="16">
+        <v>2575.72</v>
+      </c>
+      <c r="H16" s="17">
+        <v>0.0100978297448</v>
+      </c>
+      <c r="I16" s="16">
+        <v>6.37</v>
       </c>
       <c r="J16" s="11" t="s">
         <v>13</v>
@@ -1295,35 +1325,35 @@
     </row>
     <row r="17" spans="2:10" ht="15" customHeight="1">
       <c r="B17" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" s="14">
+        <v>6.33</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17" s="15">
+        <v>413500</v>
+      </c>
+      <c r="G17" s="16">
+        <v>416.92</v>
+      </c>
+      <c r="H17" s="17">
+        <v>0.0016344894543</v>
+      </c>
+      <c r="I17" s="16">
+        <v>6.31</v>
       </c>
       <c r="J17" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="18" spans="2:10" ht="15" customHeight="1">
-      <c r="B18" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="H18" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="I18" s="9" t="s">
+      <c r="B18" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J18" s="11" t="s">
@@ -1331,7 +1361,28 @@
       </c>
     </row>
     <row r="19" spans="2:10" ht="15" customHeight="1">
-      <c r="B19" s="12" t="s">
+      <c r="B19" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="I19" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J19" s="11" t="s">
@@ -1339,28 +1390,7 @@
       </c>
     </row>
     <row r="20" spans="2:10" ht="15" customHeight="1">
-      <c r="B20" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G20" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="H20" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="I20" s="9" t="s">
+      <c r="B20" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J20" s="11" t="s">
@@ -1368,7 +1398,28 @@
       </c>
     </row>
     <row r="21" spans="2:10" ht="15" customHeight="1">
-      <c r="B21" s="12" t="s">
+      <c r="B21" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="I21" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J21" s="11" t="s">
@@ -1376,28 +1427,7 @@
       </c>
     </row>
     <row r="22" spans="2:10" ht="15" customHeight="1">
-      <c r="B22" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G22" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="H22" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="I22" s="9" t="s">
+      <c r="B22" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J22" s="11" t="s">
@@ -1405,7 +1435,28 @@
       </c>
     </row>
     <row r="23" spans="2:10" ht="15" customHeight="1">
-      <c r="B23" s="12" t="s">
+      <c r="B23" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="I23" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J23" s="11" t="s">
@@ -1413,28 +1464,7 @@
       </c>
     </row>
     <row r="24" spans="2:10" ht="15" customHeight="1">
-      <c r="B24" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G24" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="H24" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="I24" s="9" t="s">
+      <c r="B24" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J24" s="11" t="s">
@@ -1442,7 +1472,28 @@
       </c>
     </row>
     <row r="25" spans="2:10" ht="15" customHeight="1">
-      <c r="B25" s="12" t="s">
+      <c r="B25" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H25" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="I25" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J25" s="11" t="s">
@@ -1450,28 +1501,7 @@
       </c>
     </row>
     <row r="26" spans="2:10" ht="15" customHeight="1">
-      <c r="B26" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F26" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G26" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="H26" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="I26" s="9" t="s">
+      <c r="B26" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J26" s="11" t="s">
@@ -1479,7 +1509,28 @@
       </c>
     </row>
     <row r="27" spans="2:10" ht="15" customHeight="1">
-      <c r="B27" s="12" t="s">
+      <c r="B27" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H27" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="I27" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J27" s="11" t="s">
@@ -1487,28 +1538,7 @@
       </c>
     </row>
     <row r="28" spans="2:10" ht="15" customHeight="1">
-      <c r="B28" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F28" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G28" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="H28" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="I28" s="9" t="s">
+      <c r="B28" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J28" s="11" t="s">
@@ -1516,7 +1546,28 @@
       </c>
     </row>
     <row r="29" spans="2:10" ht="15" customHeight="1">
-      <c r="B29" s="12" t="s">
+      <c r="B29" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H29" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="I29" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J29" s="11" t="s">
@@ -1524,28 +1575,7 @@
       </c>
     </row>
     <row r="30" spans="2:10" ht="15" customHeight="1">
-      <c r="B30" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F30" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G30" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="H30" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="I30" s="9" t="s">
+      <c r="B30" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J30" s="11" t="s">
@@ -1553,7 +1583,28 @@
       </c>
     </row>
     <row r="31" spans="2:10" ht="15" customHeight="1">
-      <c r="B31" s="12" t="s">
+      <c r="B31" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H31" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="I31" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J31" s="11" t="s">
@@ -1561,28 +1612,7 @@
       </c>
     </row>
     <row r="32" spans="2:10" ht="15" customHeight="1">
-      <c r="B32" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F32" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G32" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="H32" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="I32" s="9" t="s">
+      <c r="B32" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J32" s="11" t="s">
@@ -1590,7 +1620,28 @@
       </c>
     </row>
     <row r="33" spans="2:10" ht="15" customHeight="1">
-      <c r="B33" s="12" t="s">
+      <c r="B33" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H33" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="I33" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J33" s="11" t="s">
@@ -1598,28 +1649,7 @@
       </c>
     </row>
     <row r="34" spans="2:10" ht="15" customHeight="1">
-      <c r="B34" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F34" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G34" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="H34" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="I34" s="9" t="s">
+      <c r="B34" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J34" s="11" t="s">
@@ -1627,7 +1657,28 @@
       </c>
     </row>
     <row r="35" spans="2:10" ht="15" customHeight="1">
-      <c r="B35" s="12" t="s">
+      <c r="B35" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G35" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H35" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="I35" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J35" s="11" t="s">
@@ -1635,28 +1686,7 @@
       </c>
     </row>
     <row r="36" spans="2:10" ht="15" customHeight="1">
-      <c r="B36" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F36" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G36" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="H36" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="I36" s="9" t="s">
+      <c r="B36" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J36" s="11" t="s">
@@ -1664,7 +1694,28 @@
       </c>
     </row>
     <row r="37" spans="2:10" ht="15" customHeight="1">
-      <c r="B37" s="12" t="s">
+      <c r="B37" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G37" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H37" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="I37" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J37" s="11" t="s">
@@ -1672,28 +1723,7 @@
       </c>
     </row>
     <row r="38" spans="2:10" ht="15" customHeight="1">
-      <c r="B38" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D38" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F38" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G38" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="H38" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="I38" s="9" t="s">
+      <c r="B38" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J38" s="11" t="s">
@@ -1701,7 +1731,28 @@
       </c>
     </row>
     <row r="39" spans="2:10" ht="15" customHeight="1">
-      <c r="B39" s="12" t="s">
+      <c r="B39" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G39" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H39" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="I39" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J39" s="11" t="s">
@@ -1709,28 +1760,7 @@
       </c>
     </row>
     <row r="40" spans="2:10" ht="15" customHeight="1">
-      <c r="B40" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F40" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G40" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="H40" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="I40" s="9" t="s">
+      <c r="B40" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J40" s="11" t="s">
@@ -1738,7 +1768,28 @@
       </c>
     </row>
     <row r="41" spans="2:10" ht="15" customHeight="1">
-      <c r="B41" s="12" t="s">
+      <c r="B41" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G41" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H41" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="I41" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J41" s="11" t="s">
@@ -1746,28 +1797,7 @@
       </c>
     </row>
     <row r="42" spans="2:10" ht="15" customHeight="1">
-      <c r="B42" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C42" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E42" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F42" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G42" s="9">
-        <v>947.46</v>
-      </c>
-      <c r="H42" s="10">
-        <v>0.0038436823163</v>
-      </c>
-      <c r="I42" s="9" t="s">
+      <c r="B42" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J42" s="11" t="s">
@@ -1775,7 +1805,28 @@
       </c>
     </row>
     <row r="43" spans="2:10" ht="15" customHeight="1">
-      <c r="B43" s="12" t="s">
+      <c r="B43" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G43" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H43" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="I43" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J43" s="11" t="s">
@@ -1783,99 +1834,110 @@
       </c>
     </row>
     <row r="44" spans="2:10" ht="15" customHeight="1">
-      <c r="B44" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="C44" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D44" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E44" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F44" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G44" s="19">
-        <v>4812.40905868003</v>
-      </c>
-      <c r="H44" s="20">
-        <v>0.019523116118822587</v>
-      </c>
-      <c r="I44" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="J44" s="21" t="s">
+      <c r="B44" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J44" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="45" spans="2:10" ht="15" customHeight="1">
-      <c r="B45" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C45" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D45" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E45" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F45" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G45" s="19">
-        <v>246497.99905868</v>
-      </c>
-      <c r="H45" s="20">
-        <v>0.9999999999997226</v>
-      </c>
-      <c r="I45" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="J45" s="21" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="48" spans="2:9" ht="15" customHeight="1">
-      <c r="B48" s="13" t="s">
+      <c r="B45" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C48" s="22"/>
-      <c r="D48" s="22"/>
-      <c r="E48" s="22"/>
-      <c r="F48" s="22"/>
-      <c r="G48" s="22"/>
-      <c r="H48" s="22"/>
-      <c r="I48" s="22"/>
-    </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1">
-      <c r="B49" s="13" t="s">
+      <c r="C45" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G45" s="9">
+        <v>3783.42</v>
+      </c>
+      <c r="H45" s="10">
+        <v>0.0148324860673</v>
+      </c>
+      <c r="I45" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J45" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10" ht="15" customHeight="1">
+      <c r="B46" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J46" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10" ht="15" customHeight="1">
+      <c r="B47" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="C49" s="22"/>
-      <c r="D49" s="22"/>
-      <c r="E49" s="22"/>
-      <c r="F49" s="22"/>
-      <c r="G49" s="22"/>
-      <c r="H49" s="22"/>
-    </row>
-    <row r="50" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B50" s="23" t="s">
+      <c r="C47" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D47" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E47" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F47" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G47" s="19">
+        <v>4068.6622058099892</v>
+      </c>
+      <c r="H47" s="20">
+        <v>0.015950747070225736</v>
+      </c>
+      <c r="I47" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="J47" s="21" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="48" spans="2:10" ht="15" customHeight="1">
+      <c r="B48" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="C50" s="22"/>
-      <c r="D50" s="22"/>
-      <c r="E50" s="22"/>
-      <c r="F50" s="22"/>
-      <c r="G50" s="22"/>
-      <c r="H50" s="22"/>
-    </row>
-    <row r="51" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B51" s="23" t="s">
+      <c r="C48" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D48" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E48" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F48" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G48" s="19">
+        <v>255076.59220581</v>
+      </c>
+      <c r="H48" s="20">
+        <v>0.9999999999996257</v>
+      </c>
+      <c r="I48" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="J48" s="21" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="51" spans="2:9" ht="15" customHeight="1">
+      <c r="B51" s="13" t="s">
         <v>42</v>
       </c>
       <c r="C51" s="22"/>
@@ -1884,9 +1946,10 @@
       <c r="F51" s="22"/>
       <c r="G51" s="22"/>
       <c r="H51" s="22"/>
-    </row>
-    <row r="52" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B52" s="23" t="s">
+      <c r="I51" s="22"/>
+    </row>
+    <row r="52" spans="2:8" ht="15" customHeight="1">
+      <c r="B52" s="13" t="s">
         <v>43</v>
       </c>
       <c r="C52" s="22"/>
@@ -1896,31 +1959,64 @@
       <c r="G52" s="22"/>
       <c r="H52" s="22"/>
     </row>
-    <row r="55" ht="15">
-      <c r="B55" s="22" t="s">
+    <row r="53" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B53" s="23" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="70" ht="15">
-      <c r="B70" s="22" t="s">
+      <c r="C53" s="22"/>
+      <c r="D53" s="22"/>
+      <c r="E53" s="22"/>
+      <c r="F53" s="22"/>
+      <c r="G53" s="22"/>
+      <c r="H53" s="22"/>
+    </row>
+    <row r="54" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B54" s="23" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="71" ht="15">
-      <c r="B71" s="22" t="s">
+      <c r="C54" s="22"/>
+      <c r="D54" s="22"/>
+      <c r="E54" s="22"/>
+      <c r="F54" s="22"/>
+      <c r="G54" s="22"/>
+      <c r="H54" s="22"/>
+    </row>
+    <row r="55" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B55" s="23" t="s">
         <v>46</v>
+      </c>
+      <c r="C55" s="22"/>
+      <c r="D55" s="22"/>
+      <c r="E55" s="22"/>
+      <c r="F55" s="22"/>
+      <c r="G55" s="22"/>
+      <c r="H55" s="22"/>
+    </row>
+    <row r="58" ht="15">
+      <c r="B58" s="22" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="73" ht="15">
+      <c r="B73" s="22" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="74" ht="15">
+      <c r="B74" s="22" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="B50:H50"/>
-    <mergeCell ref="B51:H51"/>
-    <mergeCell ref="B52:H52"/>
+    <mergeCell ref="B53:H53"/>
+    <mergeCell ref="B54:H54"/>
+    <mergeCell ref="B55:H55"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B48:I48"/>
-    <mergeCell ref="B49:H49"/>
+    <mergeCell ref="B51:I51"/>
+    <mergeCell ref="B52:H52"/>
   </mergeCells>
   <printOptions gridLines="1" headings="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
